--- a/complex_test.xlsx
+++ b/complex_test.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="技能配置" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="装备表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="怪物表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="角色属性" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="技能配置备份" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能配置" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色属性" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能配置备份" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,13 +21,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -50,8 +53,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,6 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -443,7 +448,6 @@
           <t>伤害</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr"/>
       <c r="F1" t="inlineStr">
         <is>
           <t>冷却时间</t>
@@ -479,7 +483,6 @@
           <t>普通</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>5</v>
       </c>
@@ -509,7 +512,6 @@
           <t>史诗</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>10</v>
       </c>
@@ -534,10 +536,11 @@
           <t>辅助</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>15</v>
       </c>
@@ -565,7 +568,6 @@
       <c r="D5" t="n">
         <v>180</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>8</v>
       </c>
@@ -593,7 +595,6 @@
       <c r="D6" t="n">
         <v>120</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>12</v>
       </c>
@@ -621,7 +622,6 @@
       <c r="D7" t="n">
         <v>250</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>20</v>
       </c>
@@ -649,7 +649,6 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>60</v>
       </c>
@@ -677,7 +676,6 @@
       <c r="D9" t="n">
         <v>160</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>7</v>
       </c>
@@ -705,7 +703,6 @@
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
         <v>300</v>
       </c>
@@ -733,7 +730,6 @@
       <c r="D11" t="n">
         <v>140</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
         <v>9</v>
       </c>
@@ -761,7 +757,6 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
         <v>120</v>
       </c>
@@ -789,7 +784,6 @@
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>45</v>
       </c>
@@ -817,7 +811,6 @@
       <c r="D14" t="n">
         <v>500</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
         <v>180</v>
       </c>
@@ -845,7 +838,6 @@
       <c r="D15" t="n">
         <v>300</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>45</v>
       </c>
@@ -857,6 +849,11 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D2:D20">
+    <cfRule type="expression" priority="1" stopIfTrue="1">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -867,6 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -930,7 +928,7 @@
           <t>武器</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
@@ -947,7 +945,6 @@
       <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -963,7 +960,7 @@
           <t>防具</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
@@ -980,7 +977,6 @@
       <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,7 +992,7 @@
           <t>武器</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>史诗</t>
         </is>
@@ -1326,6 +1322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1693,7 +1690,6 @@
       <c r="F11" t="n">
         <v>15</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>80</v>
       </c>
@@ -1724,7 +1720,6 @@
       <c r="F12" t="n">
         <v>300</v>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>600</v>
       </c>
@@ -1778,6 +1773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2185,6 +2181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2193,13 +2190,6 @@
           <t>技能ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2220,7 +2210,6 @@
           <t>普通</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>5</v>
       </c>
@@ -2248,7 +2237,6 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>30</v>
       </c>
@@ -2278,7 +2266,6 @@
           <t>史诗</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>10</v>
       </c>
@@ -2306,7 +2293,6 @@
       <c r="D5" t="n">
         <v>100</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>15</v>
       </c>
@@ -2334,7 +2320,6 @@
       <c r="D6" t="n">
         <v>180</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>8</v>
       </c>
@@ -2362,7 +2347,6 @@
       <c r="D7" t="n">
         <v>120</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>12</v>
       </c>
@@ -2390,7 +2374,6 @@
       <c r="D8" t="n">
         <v>250</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>20</v>
       </c>
@@ -2418,7 +2401,6 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>60</v>
       </c>
@@ -2446,7 +2428,6 @@
       <c r="D10" t="n">
         <v>160</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
         <v>7</v>
       </c>
@@ -2474,7 +2455,6 @@
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
         <v>300</v>
       </c>
@@ -2502,7 +2482,6 @@
       <c r="D12" t="n">
         <v>140</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
         <v>9</v>
       </c>
@@ -2530,7 +2509,6 @@
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>25</v>
       </c>
@@ -2558,7 +2536,6 @@
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
         <v>120</v>
       </c>
@@ -2586,7 +2563,6 @@
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>45</v>
       </c>
@@ -2614,7 +2590,6 @@
       <c r="D16" t="n">
         <v>500</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>180</v>
       </c>
@@ -2642,7 +2617,6 @@
       <c r="D17" t="n">
         <v>300</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>45</v>
       </c>
